--- a/Java25_Dat_Phung_Database_Design.xlsx
+++ b/Java25_Dat_Phung_Database_Design.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="254">
   <si>
     <t>MATHANG</t>
   </si>
@@ -36,6 +36,9 @@
     <t>NhanVien</t>
   </si>
   <si>
+    <t>MatHang_Variant</t>
+  </si>
+  <si>
     <t>MaMH</t>
   </si>
   <si>
@@ -63,6 +66,9 @@
     <t>HoTen</t>
   </si>
   <si>
+    <t>GiaBan</t>
+  </si>
+  <si>
     <t>DiaChi</t>
   </si>
   <si>
@@ -72,16 +78,13 @@
     <t>Email</t>
   </si>
   <si>
-    <t>GiaBan</t>
+    <t>GiaMua</t>
   </si>
   <si>
     <t>SoDienThoai</t>
   </si>
   <si>
     <t>LoaiHang</t>
-  </si>
-  <si>
-    <t>GiaMua</t>
   </si>
   <si>
     <t>NgayDat</t>
@@ -1530,7 +1533,8 @@
     <col customWidth="1" min="4" max="4" width="14.0"/>
     <col customWidth="1" min="5" max="5" width="24.86"/>
     <col customWidth="1" min="6" max="6" width="15.86"/>
-    <col customWidth="1" min="7" max="8" width="12.71"/>
+    <col customWidth="1" min="7" max="7" width="21.14"/>
+    <col customWidth="1" min="8" max="8" width="12.71"/>
     <col customWidth="1" min="9" max="9" width="19.29"/>
     <col customWidth="1" min="10" max="11" width="12.71"/>
     <col customWidth="1" min="12" max="26" width="8.71"/>
@@ -1552,7 +1556,9 @@
       <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -1560,21 +1566,23 @@
     </row>
     <row r="5" ht="18.0" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -1582,21 +1590,23 @@
     </row>
     <row r="6" ht="18.0" customHeight="1">
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -1604,19 +1614,19 @@
     </row>
     <row r="7" ht="18.0" customHeight="1">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1626,19 +1636,19 @@
     </row>
     <row r="8" ht="18.0" customHeight="1">
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1647,17 +1657,15 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -1669,13 +1677,13 @@
     <row r="10" ht="18.0" customHeight="1">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1687,13 +1695,13 @@
     <row r="11" ht="18.0" customHeight="1">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -1705,11 +1713,11 @@
     <row r="12" ht="18.0" customHeight="1">
       <c r="B12" s="4"/>
       <c r="C12" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -1721,7 +1729,7 @@
     <row r="13" ht="18.0" customHeight="1">
       <c r="B13" s="4"/>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1735,7 +1743,7 @@
     <row r="14" ht="18.0" customHeight="1">
       <c r="B14" s="4"/>
       <c r="C14" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1749,7 +1757,7 @@
     <row r="15" ht="18.0" customHeight="1">
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1823,7 +1831,7 @@
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -2862,15 +2870,15 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="10"/>
       <c r="O2" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -2878,7 +2886,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2886,7 +2894,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4" s="11"/>
     </row>
@@ -2895,212 +2903,212 @@
     </row>
     <row r="7">
       <c r="B7" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="13"/>
       <c r="G7" s="14" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="13"/>
       <c r="P8" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O9" s="18" t="s">
         <v>1</v>
       </c>
       <c r="P9" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" s="17">
         <v>10.1</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N10" s="17">
         <v>20.0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q10" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
       <c r="G11" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H11" s="17">
         <v>10.1</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N11" s="17">
         <v>30.0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
       <c r="G12" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H12" s="17">
         <v>10.1</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N12" s="17">
         <v>60.0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="B13" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P13" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R13" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="D14" s="13"/>
       <c r="O14" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P14" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -3108,11 +3116,11 @@
     </row>
     <row r="17">
       <c r="B17" s="24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="13"/>
       <c r="G17" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="13"/>
@@ -3120,10 +3128,10 @@
         <v>1.0</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -3131,39 +3139,39 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="N18" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" s="16" t="s">
         <v>1</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20">
@@ -3171,19 +3179,19 @@
         <v>1.0</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" s="13">
         <v>1.0</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J20" s="17">
         <v>5.0</v>
@@ -3191,22 +3199,22 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G21" s="13">
         <v>2.0</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J21" s="17">
         <v>7.0</v>
@@ -3215,10 +3223,10 @@
         <v>2.0</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -3226,26 +3234,26 @@
         <v>3.0</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="13">
         <v>3.0</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J22" s="17">
         <v>1.0</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -3253,16 +3261,16 @@
         <v>4.0</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J23" s="17">
         <v>4.0</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -3270,10 +3278,10 @@
         <v>5.0</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J24" s="17">
         <v>6.0</v>
@@ -3284,10 +3292,10 @@
         <v>6.0</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J25" s="26">
         <v>2.0</v>
@@ -3298,10 +3306,10 @@
         <v>7.0</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J26" s="26">
         <v>4.0</v>
@@ -3310,28 +3318,28 @@
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>3</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="C30" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
@@ -3340,19 +3348,19 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="C33" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -4376,79 +4384,79 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
       <c r="E3" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
       <c r="E4" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P4" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T4" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U4" s="31"/>
     </row>
     <row r="5">
       <c r="E5" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="V5" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X5" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y5" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="E6" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q6" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R6" s="17">
         <v>20.0</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V6" s="17"/>
       <c r="W6" s="17"/>
@@ -4459,22 +4467,22 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R7" s="17">
         <v>30.0</v>
       </c>
       <c r="T7" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U7" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V7" s="17"/>
       <c r="W7" s="17"/>
@@ -4485,22 +4493,22 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R8" s="17">
         <v>60.0</v>
       </c>
       <c r="T8" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V8" s="17"/>
       <c r="W8" s="17"/>
@@ -4511,13 +4519,13 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V9" s="17"/>
       <c r="W9" s="17"/>
@@ -4528,7 +4536,7 @@
     </row>
     <row r="10">
       <c r="C10" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -4541,13 +4549,13 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="P10" s="32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="V10" s="17"/>
       <c r="W10" s="17"/>
@@ -4558,20 +4566,20 @@
     </row>
     <row r="11">
       <c r="C11" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R11" s="13"/>
       <c r="T11" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V11" s="17"/>
       <c r="W11" s="17"/>
@@ -4582,40 +4590,40 @@
     </row>
     <row r="12">
       <c r="P12" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q12" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R12" s="13"/>
     </row>
     <row r="13">
       <c r="P13" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q13" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R13" s="13"/>
       <c r="T13" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
       <c r="P14" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q14" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R14" s="13"/>
       <c r="T14" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="T15" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
@@ -4632,7 +4640,7 @@
     </row>
     <row r="18">
       <c r="T18" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U18" s="32"/>
       <c r="V18" s="32"/>
@@ -4640,41 +4648,41 @@
     </row>
     <row r="19">
       <c r="P19" s="34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q19" s="35"/>
       <c r="T19" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="V19" s="17" t="s">
         <v>4</v>
       </c>
       <c r="W19" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="P20" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q20" s="36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R20" s="37"/>
       <c r="T20" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U20" s="17">
         <v>1.0</v>
       </c>
       <c r="V20" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W20" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -4682,20 +4690,20 @@
         <v>1.0</v>
       </c>
       <c r="Q21" s="36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R21" s="37"/>
       <c r="T21" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U21" s="17">
         <v>2.0</v>
       </c>
       <c r="V21" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W21" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -4703,20 +4711,20 @@
         <v>2.0</v>
       </c>
       <c r="Q22" s="36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R22" s="37"/>
       <c r="T22" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U22" s="17">
         <v>3.0</v>
       </c>
       <c r="V22" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W22" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -4724,7 +4732,7 @@
         <v>3.0</v>
       </c>
       <c r="Q23" s="36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R23" s="37"/>
       <c r="T23" s="17"/>
@@ -4732,13 +4740,13 @@
       <c r="V23" s="17"/>
       <c r="W23" s="17"/>
       <c r="AG23" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AH23" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AI23" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -4746,26 +4754,26 @@
         <v>4.0</v>
       </c>
       <c r="Q24" s="36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R24" s="37"/>
       <c r="T24" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="U24" s="17">
         <v>1.0</v>
       </c>
       <c r="V24" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W24" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG24" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AH24" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
@@ -4773,18 +4781,18 @@
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1">
       <c r="T28" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U28" s="33"/>
       <c r="X28" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y28" s="33"/>
       <c r="AA28" s="31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD28" s="38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AF28" s="31" t="s">
         <v>1</v>
@@ -4792,375 +4800,375 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="C29" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H29" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="P29" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="J29" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="P29" s="32" t="s">
-        <v>148</v>
-      </c>
       <c r="T29" s="40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U29" s="40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V29" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="X29" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y29" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA29" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AB29" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AC29" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD29" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF29" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG29" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="AD29" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF29" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG29" s="17" t="s">
-        <v>154</v>
-      </c>
       <c r="AH29" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AI29" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="C30" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D30" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="J30" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="J30" s="42" t="s">
-        <v>157</v>
-      </c>
       <c r="K30" s="43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L30" s="43"/>
       <c r="M30" s="43"/>
       <c r="P30" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q30" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="V30" s="4">
         <v>5.0</v>
       </c>
       <c r="X30" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y30" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA30" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AB30" s="44" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AC30" s="17">
         <v>225.0</v>
       </c>
       <c r="AD30" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF30" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG30" s="44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AH30" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AI30" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="C31" s="41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E31" s="41">
         <v>8.0</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H31" s="41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="J31" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="J31" s="45" t="s">
-        <v>162</v>
-      </c>
       <c r="K31" s="46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L31" s="47"/>
       <c r="M31" s="43"/>
       <c r="P31" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q31" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R31" s="6">
         <v>7.8</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="V31" s="4">
         <v>6.0</v>
       </c>
       <c r="X31" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y31" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA31" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB31" s="44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AC31" s="17">
         <v>0.0</v>
       </c>
       <c r="AD31" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF31" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AG31" s="44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AH31" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AI31" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="C32" s="41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" s="41">
         <v>6.0</v>
       </c>
       <c r="F32" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I32" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="J32" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="H32" s="41" t="s">
+      <c r="P32" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="I32" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="J32" s="45" t="s">
-        <v>170</v>
-      </c>
-      <c r="P32" s="17" t="s">
-        <v>170</v>
-      </c>
       <c r="Q32" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R32" s="6">
         <v>8.0</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="V32" s="4">
         <v>7.0</v>
       </c>
       <c r="X32" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y32" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AA32" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AB32" s="44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AC32" s="17">
         <v>125.0</v>
       </c>
       <c r="AD32" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF32" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG32" s="44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AH32" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AI32" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="C33" s="41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E33" s="41">
         <v>9.0</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H33" s="41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I33" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J33" s="45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q33" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R33" s="6">
         <v>9.5</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V33" s="4">
         <v>5.0</v>
       </c>
       <c r="AA33" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AB33" s="44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AC33" s="17">
         <v>220.0</v>
       </c>
       <c r="AD33" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AF33" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG33" s="44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AH33" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AI33" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="C34" s="41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E34" s="41">
         <v>7.0</v>
       </c>
       <c r="F34" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="P34" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q34" s="17" t="s">
         <v>190</v>
-      </c>
-      <c r="P34" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q34" s="17" t="s">
-        <v>189</v>
       </c>
       <c r="R34" s="6">
         <v>2.0</v>
       </c>
       <c r="T34" s="48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U34" s="48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="V34" s="4">
         <v>9.0</v>
@@ -5168,22 +5176,22 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="C35" s="41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E35" s="41">
         <v>7.0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P35" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q35" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R35" s="6">
         <v>4.6</v>
@@ -5192,7 +5200,7 @@
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1">
       <c r="C37" s="49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
@@ -5204,7 +5212,7 @@
       <c r="K37" s="27"/>
       <c r="L37" s="27"/>
       <c r="P37" s="49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q37" s="27"/>
       <c r="R37" s="27"/>
@@ -5213,7 +5221,7 @@
       <c r="U37" s="27"/>
       <c r="V37" s="27"/>
       <c r="AA37" s="27" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AB37" s="27"/>
       <c r="AC37" s="27"/>
@@ -5227,51 +5235,51 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="C38" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA38" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="C39" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA39" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="C40" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P40" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AA40" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="C41" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA41" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="C42" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA42" s="51" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AB42" s="51"/>
       <c r="AC42" s="51"/>
@@ -5283,58 +5291,58 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="C43" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="C44" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O44" s="52" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T44" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y44" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="C45" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O45" s="53" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q45" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="T45" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="U45" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="R45" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="T45" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="U45" s="8" t="s">
-        <v>211</v>
-      </c>
       <c r="V45" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Y45" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="C46" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O46" s="4">
         <v>1.0</v>
@@ -5343,13 +5351,13 @@
         <v>1.0</v>
       </c>
       <c r="Q46" s="54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R46" s="54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U46" s="4">
         <v>1.0</v>
@@ -5358,15 +5366,15 @@
         <v>8.0</v>
       </c>
       <c r="Y46" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AE46" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="C47" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O47" s="4">
         <v>2.0</v>
@@ -5375,13 +5383,13 @@
         <v>2.0</v>
       </c>
       <c r="Q47" s="54" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="R47" s="54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U47" s="4">
         <v>2.0</v>
@@ -5390,15 +5398,15 @@
         <v>8.0</v>
       </c>
       <c r="Y47" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF47" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="C48" s="55" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O48" s="4">
         <v>3.0</v>
@@ -5407,13 +5415,13 @@
         <v>3.0</v>
       </c>
       <c r="Q48" s="54" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R48" s="54" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U48" s="4">
         <v>1.0</v>
@@ -5422,15 +5430,15 @@
         <v>9.0</v>
       </c>
       <c r="AE48" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AF48" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" ht="32.25" customHeight="1">
       <c r="C49" s="56" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O49" s="4">
         <v>4.0</v>
@@ -5439,13 +5447,13 @@
         <v>4.0</v>
       </c>
       <c r="Q49" s="54" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R49" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U49" s="4">
         <v>1.0</v>
@@ -5454,10 +5462,10 @@
         <v>9.0</v>
       </c>
       <c r="AE49" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AF49" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -5468,16 +5476,16 @@
         <v>5.0</v>
       </c>
       <c r="Q50" s="54" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="R50" s="54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AE50" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF50" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -5488,24 +5496,24 @@
         <v>6.0</v>
       </c>
       <c r="Q51" s="54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R51" s="54" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AE51" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AF51" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="C52" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O52" s="4">
         <v>7.0</v>
@@ -5514,39 +5522,39 @@
         <v>7.0</v>
       </c>
       <c r="Q52" s="54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R52" s="54" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AE52" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AF52" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="C53" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D53" s="41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I53" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O53" s="4">
         <v>8.0</v>
@@ -5555,24 +5563,24 @@
         <v>8.0</v>
       </c>
       <c r="Q53" s="54" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R53" s="54" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="C54" s="41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E54" s="41">
         <v>8.0</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H54" s="41"/>
       <c r="I54" s="41"/>
@@ -5583,36 +5591,36 @@
         <v>1.0</v>
       </c>
       <c r="Q54" s="54" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="R54" s="54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="C55" s="41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E55" s="41">
         <v>6.0</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H55" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I55" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="J55" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="I55" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>170</v>
-      </c>
       <c r="N55" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O55" s="4">
         <v>10.0</v>
@@ -5621,33 +5629,33 @@
         <v>2.0</v>
       </c>
       <c r="Q55" s="54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R55" s="54" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="C56" s="41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D56" s="41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E56" s="41">
         <v>9.0</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H56" s="41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I56" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O56" s="4">
         <v>11.0</v>
@@ -5656,24 +5664,24 @@
         <v>3.0</v>
       </c>
       <c r="Q56" s="54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R56" s="54" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="C57" s="41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E57" s="41">
         <v>7.0</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O57" s="4">
         <v>12.0</v>
@@ -5682,24 +5690,24 @@
         <v>4.0</v>
       </c>
       <c r="Q57" s="54" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R57" s="54" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="C58" s="41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D58" s="41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E58" s="41">
         <v>7.0</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O58" s="4">
         <v>13.0</v>
@@ -5708,10 +5716,10 @@
         <v>5.0</v>
       </c>
       <c r="Q58" s="54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R58" s="54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
@@ -5722,10 +5730,10 @@
         <v>6.0</v>
       </c>
       <c r="Q59" s="54" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="R59" s="54" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -5736,10 +5744,10 @@
         <v>7.0</v>
       </c>
       <c r="Q60" s="54" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R60" s="54" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -5750,10 +5758,10 @@
         <v>8.0</v>
       </c>
       <c r="Q61" s="54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R61" s="54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1"/>
@@ -5767,113 +5775,113 @@
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1">
       <c r="Q71" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W71" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X71" s="33"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="Q72" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R72" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S72" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T72" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="W72" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X72" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="Q73" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R73" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S73" s="6">
         <v>7.8</v>
       </c>
       <c r="T73" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="W73" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="X73" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="Q74" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R74" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S74" s="6">
         <v>8.0</v>
       </c>
       <c r="T74" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="W74" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="X74" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="Q75" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R75" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S75" s="6">
         <v>9.5</v>
       </c>
       <c r="T75" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="W75" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="X75" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="Q76" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="R76" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="S76" s="6">
         <v>2.0</v>
       </c>
       <c r="T76" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="Q77" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="R77" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S77" s="6">
         <v>4.6</v>
@@ -6840,7 +6848,7 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
@@ -7103,23 +7111,23 @@
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1">
       <c r="B26" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>

--- a/Java25_Dat_Phung_Database_Design.xlsx
+++ b/Java25_Dat_Phung_Database_Design.xlsx
@@ -3,124 +3,505 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Mô hình quan niệm" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="ERD - Mô hình logic" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="RD - Mô hình quan hệ" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="DB - Mô hình vật lý" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="1. Mô hình quan niệm" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="2. Mô hình logic" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="ERD - Mô hình logic" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="RD - Mô hình quan hệ" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="DB - Mô hình vật lý" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="p5BS4hUL/OOE04XVfIKJjWpietQKE5HphlkPzTEkUkA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="kq60OLfSwC1eKTtsP2NmM4uA6N6qpMtIWGEHanoLG7o="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="I7">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_YkkpbI
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+LoaiHangPhu thuộc LoaiHang</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B15">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_Ykkpa8
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+xem chỗ LoaiHang</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B14">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_YkkpbU
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+MatHang thuộc trực tiếp LoaiHang || thông qua LoaiHangPhu mới đến LoaiHang, nullable</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C15">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_YkkpbQ
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+Thuộc tính dẫn xuất</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C12">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_YkkpbM
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+Thuộc tính dẫn xuất</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B10">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_YkkpbE
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+Lưu trữ theo MatHang, KichThuoc</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B9">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_YkkpbY
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+GiaBan phụ thuộc vào KichThuoc</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B8">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAB_YkkpbA
+Quyen Ngoc Phan    (2026-07-08 08:48:15)
+Muốn lưu trữ lịch sử giá mua từ các nhà cung cấp theo thời gian</t>
+      </text>
+    </comment>
+  </commentList>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7migbS9+8j0LiItM9VHFtREya6Tgkw=="/>
+    </ext>
+  </extLst>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="254">
-  <si>
-    <t>MATHANG</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="300">
+  <si>
+    <t>BLOB CLOB</t>
+  </si>
+  <si>
+    <t>MatHang</t>
   </si>
   <si>
     <t>DonHang</t>
   </si>
   <si>
-    <t>Variant</t>
-  </si>
-  <si>
     <t>KhachHang</t>
   </si>
   <si>
+    <t>SanPham</t>
+  </si>
+  <si>
     <t>NhanVien</t>
   </si>
   <si>
-    <t>MatHang_Variant</t>
+    <t>LichSuTrangThai</t>
+  </si>
+  <si>
+    <t>NhaSanXuat</t>
+  </si>
+  <si>
+    <t>LoaiHangLon</t>
+  </si>
+  <si>
+    <t>LoaiHangNho</t>
   </si>
   <si>
     <t>MaMH</t>
   </si>
   <si>
-    <t>MaDonHang</t>
-  </si>
-  <si>
-    <t>MaVariant</t>
-  </si>
-  <si>
-    <t>MaKhachHang</t>
-  </si>
-  <si>
-    <t>MaNhanVien</t>
-  </si>
-  <si>
-    <t>TinhTrang</t>
-  </si>
-  <si>
-    <t>TenNguoiDatHang</t>
+    <t>MaDH</t>
+  </si>
+  <si>
+    <t>MaKH</t>
+  </si>
+  <si>
+    <t>QuanAoNam</t>
+  </si>
+  <si>
+    <t>HoTen</t>
+  </si>
+  <si>
+    <t>TenNSX</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>TenMH</t>
+  </si>
+  <si>
+    <t>QuanAoNu</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>TrangThai</t>
+  </si>
+  <si>
+    <t>MaNSX</t>
+  </si>
+  <si>
+    <t>KichThuoc</t>
+  </si>
+  <si>
+    <t>TenNguoiDat</t>
+  </si>
+  <si>
+    <t>QuanAoTreEm</t>
+  </si>
+  <si>
+    <t>SDT</t>
+  </si>
+  <si>
+    <t>NguoiXuLyDonHang</t>
+  </si>
+  <si>
+    <t>GiaMua</t>
+  </si>
+  <si>
+    <t>DiaChiGiaoHang</t>
+  </si>
+  <si>
+    <t>SDTKhachHang</t>
+  </si>
+  <si>
+    <t>PhanQuyen</t>
+  </si>
+  <si>
+    <t>ThoiGian</t>
+  </si>
+  <si>
+    <t>ThuocLoaiHangLon</t>
+  </si>
+  <si>
+    <t>GiaBan</t>
+  </si>
+  <si>
+    <t>SDTNguoiNhan</t>
+  </si>
+  <si>
+    <t>DNMangXaHoi</t>
+  </si>
+  <si>
+    <t>SoLuongTonKho</t>
+  </si>
+  <si>
+    <t>NgayDatHang</t>
+  </si>
+  <si>
+    <t>MatKhau</t>
+  </si>
+  <si>
+    <t>MaLoai</t>
+  </si>
+  <si>
+    <t>NgayGiaoHang</t>
+  </si>
+  <si>
+    <t>ChatLieu</t>
+  </si>
+  <si>
+    <t>TongSoLuongHang</t>
   </si>
   <si>
     <t>MauSac</t>
   </si>
   <si>
-    <t>HoTen</t>
-  </si>
-  <si>
-    <t>GiaBan</t>
-  </si>
-  <si>
-    <t>DiaChi</t>
-  </si>
-  <si>
-    <t>KichThuoc</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>GiaMua</t>
-  </si>
-  <si>
-    <t>SoDienThoai</t>
+    <t>PhiVanChuyen</t>
+  </si>
+  <si>
+    <t>TongTien</t>
+  </si>
+  <si>
+    <t>PhuongThucThanhToan</t>
+  </si>
+  <si>
+    <t>ChiTietCacMatHang</t>
+  </si>
+  <si>
+    <t>1. Xác định các đối tượng và thuộc tính(thông tin cần lưu trữ)</t>
+  </si>
+  <si>
+    <t>Đối tượng: thực thể trong thế giới thực, gồm 1 hoặc N thuộc tính</t>
+  </si>
+  <si>
+    <t>Thuộc tính: 1 thông tin, đơn vị nhỏ nhất có thể lưu trữ và thuộc đối tượng</t>
+  </si>
+  <si>
+    <t>Webpage: Hỗ trợ mua bán sản phẩm quần áo online, không hỗ trợ giao dịch trực tiếp tại cửa hàng</t>
   </si>
   <si>
     <t>LoaiHang</t>
   </si>
   <si>
-    <t>NgayDat</t>
-  </si>
-  <si>
-    <t>TenMH</t>
-  </si>
-  <si>
-    <t>provider: SOCIAL_MEDIA</t>
-  </si>
-  <si>
-    <t>TongSoLuong</t>
-  </si>
-  <si>
-    <t>ChatLieu</t>
-  </si>
-  <si>
-    <t>TongTien</t>
-  </si>
-  <si>
-    <t>SoLuong</t>
-  </si>
-  <si>
-    <t>MatKhau</t>
-  </si>
-  <si>
-    <t>PhiVanChuyen</t>
-  </si>
-  <si>
-    <t>provider_id</t>
-  </si>
-  <si>
-    <t>LoaiHinhThanhToan</t>
-  </si>
-  <si>
-    <t>1. Xác định các đối tượng và thông tin cần lưu trữ</t>
+    <t>LoaiHangPhu</t>
+  </si>
+  <si>
+    <t>MaNV</t>
+  </si>
+  <si>
+    <t>MaLH</t>
+  </si>
+  <si>
+    <t>MaLHP</t>
+  </si>
+  <si>
+    <t>MaKT</t>
+  </si>
+  <si>
+    <t>MaPTTT</t>
+  </si>
+  <si>
+    <t>TenLH</t>
+  </si>
+  <si>
+    <t>TenLHP</t>
+  </si>
+  <si>
+    <t>GioiTinh</t>
+  </si>
+  <si>
+    <t>MoTa</t>
+  </si>
+  <si>
+    <t>KichThuoc(s)</t>
+  </si>
+  <si>
+    <t>ChatLieu(s)</t>
+  </si>
+  <si>
+    <t>NgayGiaoHangDuKien</t>
+  </si>
+  <si>
+    <t>MauSac(s)</t>
+  </si>
+  <si>
+    <t>HinhAnh(s)</t>
+  </si>
+  <si>
+    <t>MatHang(s)</t>
+  </si>
+  <si>
+    <t>Mô hình quan niệm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>đối tượng</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve"> của dự án</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">2. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>thông tin</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve"> cần lưu trữ của từng đối tượng</t>
+    </r>
+  </si>
+  <si>
+    <t>Mô hình logic(trên cơ sở đối tượng, mẫu tin)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>tập thực thể</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">2. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>thuộc tính</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve"> của mỗi tập thực thể(đơn trị, đa trị, kết hợp, dẫn xuất)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** KDL nguyên tố(ngày tháng năm, chuỗi, số, luận lý) không thể là danh sách, đối tượng</t>
+  </si>
+  <si>
+    <t>Áo thun</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">3. Xác định </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>khóa</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve"> của mỗi tập thực thể</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Khóa là tập ít nhất các thuộc tính dùng để phân biệt 2/N thực thể khác nhau trong 1 tập thực thể</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Đảm bảo dữ liệu không trùng nhau, vô nghĩa, tốn vùng nhớ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Hỗ trợ truy vấn nhanh hơn so với các thuộc tính thông thường</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+      </rPr>
+      <t>4. Xác định</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve"> mối kết hợp</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve"> giữa các tập thực thể</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Thông qua các cặp số min, max rồi chọn max ở mỗi bên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Có ba loại mối kết hợp: 11 1n n1 nn, tạo ràng buộc cho các tập thực thể cũng như thiết kế ra CSDL vật lý có thể lưu trữ dữ liệu chính xác</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">    ** </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1o31TYiTt0vtiiV8sPzlnUwWWCUoZyVcG/view?usp=sharing</t>
+    </r>
   </si>
   <si>
     <t>Khóa là tập ít nhất các thuộc tính(column) dùng để phân biệt 2 thực thể(table) với nhau</t>
@@ -163,9 +544,6 @@
     <t>SinhVien</t>
   </si>
   <si>
-    <t>MatHang</t>
-  </si>
-  <si>
     <t>n-n</t>
   </si>
   <si>
@@ -191,12 +569,6 @@
   </si>
   <si>
     <t>TenSV</t>
-  </si>
-  <si>
-    <t>MaDH</t>
-  </si>
-  <si>
-    <t>NgayDatHang</t>
   </si>
   <si>
     <t>DiaChiGiao</t>
@@ -370,9 +742,6 @@
     </r>
   </si>
   <si>
-    <t>MaLH</t>
-  </si>
-  <si>
     <t>TenLop</t>
   </si>
   <si>
@@ -382,6 +751,9 @@
     <t>MaCTDH</t>
   </si>
   <si>
+    <t>SoLuong</t>
+  </si>
+  <si>
     <t>Index</t>
   </si>
   <si>
@@ -484,9 +856,6 @@
     <t>Kết quả của Mối Quan Hệ &gt;&gt;&gt; 1-1 &gt;&gt; Tạo thêm column (Khóa Ngoại) - Bỏ bên nào cũng được. Nhưng … Unique … Xác định logic phù hợp</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t xml:space="preserve">        &gt;&gt;&gt; 1-n &gt;&gt; Tạo thêm column (Khóa Ngoại) bên bảng N liên kết với Khóa Chính bên Bảng 1 </t>
   </si>
   <si>
@@ -499,9 +868,6 @@
     <t xml:space="preserve">        &gt;&gt;&gt; n-n &gt;&gt; Tạo thêm bảng mới. Khóa chính là tập các thuộc tính là khóa chính ở n bảng liên kết</t>
   </si>
   <si>
-    <t>MoTa</t>
-  </si>
-  <si>
     <t>XMT</t>
   </si>
   <si>
@@ -527,9 +893,6 @@
   </si>
   <si>
     <t>MaTT</t>
-  </si>
-  <si>
-    <t>ThoiGian</t>
   </si>
   <si>
     <t>DH1</t>
@@ -779,9 +1142,6 @@
     <t>FK: foreign key</t>
   </si>
   <si>
-    <t>MaKH</t>
-  </si>
-  <si>
     <t>BatDau</t>
   </si>
   <si>
@@ -909,9 +1269,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="13">
+  <fonts count="21">
     <font>
       <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -922,9 +1287,41 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF8496B0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF2E75B5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -933,9 +1330,19 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11.0"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font/>
     <font>
@@ -947,12 +1354,6 @@
       <strike/>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11.0"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -980,7 +1381,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -991,6 +1392,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD6EE"/>
+        <bgColor rgb="FFBDD6EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1119,158 +1526,185 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="70">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="16" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="16" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf quotePrefix="1" borderId="2" fillId="4" fontId="1" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="2" fillId="5" fontId="2" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="7" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf borderId="2" fillId="6" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="9" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="12" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf quotePrefix="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf quotePrefix="1" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="1" fillId="0" fontId="1" numFmtId="17" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="1" fillId="0" fontId="2" numFmtId="17" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1294,6 +1728,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1528,145 +1966,168 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.71"/>
-    <col customWidth="1" min="2" max="2" width="15.57"/>
-    <col customWidth="1" min="3" max="3" width="18.43"/>
-    <col customWidth="1" min="4" max="4" width="14.0"/>
-    <col customWidth="1" min="5" max="5" width="24.86"/>
-    <col customWidth="1" min="6" max="6" width="15.86"/>
-    <col customWidth="1" min="7" max="7" width="21.14"/>
-    <col customWidth="1" min="8" max="8" width="12.71"/>
-    <col customWidth="1" min="9" max="9" width="19.29"/>
-    <col customWidth="1" min="10" max="11" width="12.71"/>
+    <col customWidth="1" min="2" max="11" width="20.71"/>
     <col customWidth="1" min="12" max="26" width="8.71"/>
   </cols>
   <sheetData>
+    <row r="2">
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="4" ht="18.0" customHeight="1">
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" ht="18.0" customHeight="1">
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K5" s="4"/>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K6" s="4"/>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K7" s="4"/>
     </row>
     <row r="8" ht="18.0" customHeight="1">
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="K8" s="4"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -1675,16 +2136,16 @@
       <c r="K9" s="4"/>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -1693,16 +2154,14 @@
       <c r="K10" s="4"/>
     </row>
     <row r="11" ht="18.0" customHeight="1">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="B11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -1711,14 +2170,14 @@
       <c r="K11" s="4"/>
     </row>
     <row r="12" ht="18.0" customHeight="1">
-      <c r="B12" s="4"/>
-      <c r="C12" s="3" t="s">
-        <v>30</v>
+      <c r="B12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -1727,9 +2186,11 @@
       <c r="K12" s="4"/>
     </row>
     <row r="13" ht="18.0" customHeight="1">
-      <c r="B13" s="4"/>
-      <c r="C13" s="3" t="s">
-        <v>32</v>
+      <c r="B13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1742,8 +2203,8 @@
     </row>
     <row r="14" ht="18.0" customHeight="1">
       <c r="B14" s="4"/>
-      <c r="C14" s="3" t="s">
-        <v>9</v>
+      <c r="C14" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1756,8 +2217,8 @@
     </row>
     <row r="15" ht="18.0" customHeight="1">
       <c r="B15" s="4"/>
-      <c r="C15" s="3" t="s">
-        <v>11</v>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1770,7 +2231,9 @@
     </row>
     <row r="16" ht="18.0" customHeight="1">
       <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
+      <c r="C16" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -1830,46 +2293,56 @@
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="B22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="B22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="B25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2857,6 +3330,1518 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="14.71"/>
+    <col customWidth="1" min="2" max="12" width="20.71"/>
+    <col customWidth="1" min="13" max="26" width="8.71"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="18.0" customHeight="1">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" ht="18.0" customHeight="1">
+      <c r="B5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" ht="18.0" customHeight="1">
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" ht="18.0" customHeight="1">
+      <c r="B7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" ht="18.0" customHeight="1">
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" ht="18.0" customHeight="1">
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" ht="18.0" customHeight="1">
+      <c r="B10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" ht="18.0" customHeight="1">
+      <c r="B11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" ht="18.0" customHeight="1">
+      <c r="B12" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" ht="18.0" customHeight="1">
+      <c r="B13" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" ht="18.0" customHeight="1">
+      <c r="B14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" ht="18.0" customHeight="1">
+      <c r="B15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" ht="18.0" customHeight="1">
+      <c r="B16" s="4"/>
+      <c r="C16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" ht="18.0" customHeight="1">
+      <c r="B17" s="4"/>
+      <c r="C17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" ht="18.0" customHeight="1">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" ht="18.0" customHeight="1">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" ht="18.0" customHeight="1">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="G22" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="10"/>
+      <c r="B24" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="B25" s="18"/>
+      <c r="G25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="B26" s="18"/>
+      <c r="G26" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="B27" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="B31" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17">
+        <v>120.0</v>
+      </c>
+      <c r="L31" s="17">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="G32" s="20">
+        <v>2.0</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20">
+        <v>122.0</v>
+      </c>
+      <c r="L32" s="20">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="B34" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="B38" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="B39" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="B41" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId2" ref="B41"/>
+  </hyperlinks>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
     <col customWidth="1" min="1" max="3" width="8.71"/>
     <col customWidth="1" min="4" max="4" width="10.0"/>
     <col customWidth="1" min="5" max="7" width="8.71"/>
@@ -2869,533 +4854,533 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="8" t="s">
-        <v>36</v>
+      <c r="B2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M2" s="22"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8">
+      <c r="A3" s="1">
         <v>1.0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P4" s="15"/>
+    </row>
+    <row r="5">
+      <c r="N5" s="15"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="G7" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="24"/>
+      <c r="P8" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="28" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8">
+      <c r="I9" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="P9" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="28">
+        <v>10.1</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="N10" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="P10" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q10" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="28">
+        <v>10.1</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" s="28">
+        <v>30.0</v>
+      </c>
+      <c r="O11" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="28">
+        <v>10.1</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="N12" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="O12" s="29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="B13" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="P13" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q13" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" s="24"/>
+      <c r="O14" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="P14" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q14" s="33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="J16" s="15"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="G17" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="25"/>
+      <c r="I17" s="24"/>
+      <c r="M17" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="N18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="28">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="24">
         <v>2.0</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="11"/>
-    </row>
-    <row r="5">
-      <c r="N5" s="11"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="13"/>
-      <c r="G7" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="13"/>
-      <c r="P8" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="M9" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O9" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="17">
-        <v>10.1</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="17">
-        <v>20.0</v>
-      </c>
-      <c r="O10" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="P10" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q10" s="21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="17">
-        <v>10.1</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="17">
-        <v>30.0</v>
-      </c>
-      <c r="O11" s="18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="17">
-        <v>10.1</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L12" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="M12" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="N12" s="17">
-        <v>60.0</v>
-      </c>
-      <c r="O12" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="B13" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="O13" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="P13" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="R13" s="23" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="D14" s="13"/>
-      <c r="O14" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="P14" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q14" s="22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="G17" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="13"/>
-      <c r="M17" s="13">
+      <c r="H21" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="28">
+        <v>7.0</v>
+      </c>
+      <c r="M21" s="24">
+        <v>2.0</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="28">
+        <v>3.0</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J22" s="28">
         <v>1.0</v>
       </c>
-      <c r="N17" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="T17" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="N18" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="T18" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="T19" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="17">
+      <c r="N22" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="G23" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" s="28">
+        <v>4.0</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="G24" s="24">
         <v>5.0</v>
       </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="13">
+      <c r="H24" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J24" s="28">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="G25" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="37">
         <v>2.0</v>
       </c>
-      <c r="H21" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="17">
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="G26" s="24">
         <v>7.0</v>
       </c>
-      <c r="M21" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="B22" s="17">
-        <v>3.0</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="J22" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="G23" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J23" s="17">
-        <v>4.0</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="G24" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="J24" s="17">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="G25" s="13">
-        <v>6.0</v>
-      </c>
-      <c r="H25" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="J25" s="26">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="G26" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="J26" s="26">
+      <c r="H26" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="J26" s="37">
         <v>4.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="B28" s="8" t="s">
-        <v>98</v>
+      <c r="B28" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="B29" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="N29" s="8" t="s">
+      <c r="B29" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="8" t="s">
-        <v>100</v>
+      <c r="R29" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="8" t="s">
-        <v>101</v>
+      <c r="C30" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="B31" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
+      <c r="B31" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="B32" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28" t="s">
-        <v>104</v>
+      <c r="B32" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="19" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="8" t="s">
-        <v>105</v>
+      <c r="C33" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>
@@ -4365,7 +6350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
@@ -4383,966 +6368,966 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>107</v>
+      <c r="A2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="3">
-      <c r="E3" s="8" t="s">
-        <v>108</v>
+      <c r="E3" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="4">
-      <c r="E4" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="P4" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="U4" s="31"/>
+      <c r="E4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P4" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="U4" s="40"/>
     </row>
     <row r="5">
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="R5" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="U5" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="V5" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="W5" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="R6" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="T6" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="U6" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="P7" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q7" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="R7" s="28">
+        <v>30.0</v>
+      </c>
+      <c r="T7" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="U7" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="P8" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="R8" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="T8" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="U8" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="T9" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="U9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="P10" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="T10" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="U10" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P11" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q11" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="R11" s="24"/>
+      <c r="T11" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="U11" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="28">
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="P12" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q12" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="R12" s="24"/>
+    </row>
+    <row r="13">
+      <c r="P13" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="R13" s="24"/>
+      <c r="T13" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="P14" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q14" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="R14" s="24"/>
+      <c r="T14" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="T15" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="38"/>
+    </row>
+    <row r="18">
+      <c r="T18" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="U18" s="41"/>
+      <c r="V18" s="41"/>
+      <c r="W18" s="24"/>
+    </row>
+    <row r="19">
+      <c r="P19" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q19" s="44"/>
+      <c r="T19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="U19" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="V19" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="W19" s="28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="P20" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q20" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="R20" s="46"/>
+      <c r="T20" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="U20" s="28">
+        <v>1.0</v>
+      </c>
+      <c r="V20" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="W20" s="28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="P21" s="28">
+        <v>1.0</v>
+      </c>
+      <c r="Q21" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="R21" s="46"/>
+      <c r="T21" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="U21" s="28">
+        <v>2.0</v>
+      </c>
+      <c r="V21" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="P5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="T5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="U5" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="V5" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="W5" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="X5" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y5" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="E6" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" s="17">
-        <v>20.0</v>
-      </c>
-      <c r="T6" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="U6" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="P7" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="R7" s="17">
-        <v>30.0</v>
-      </c>
-      <c r="T7" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="U7" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="s">
+      <c r="W21" s="28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="P22" s="28">
+        <v>2.0</v>
+      </c>
+      <c r="Q22" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="R22" s="46"/>
+      <c r="T22" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="U22" s="28">
+        <v>3.0</v>
+      </c>
+      <c r="V22" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="W22" s="28" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="P23" s="28">
+        <v>3.0</v>
+      </c>
+      <c r="Q23" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="R23" s="46"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="AG23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="P24" s="28">
+        <v>4.0</v>
+      </c>
+      <c r="Q24" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="R24" s="46"/>
+      <c r="T24" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="U24" s="28">
+        <v>1.0</v>
+      </c>
+      <c r="V24" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="P8" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="R8" s="17">
-        <v>60.0</v>
-      </c>
-      <c r="T8" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="U8" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="U9" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="P10" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="U10" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17">
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q11" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="R11" s="13"/>
-      <c r="T11" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="U11" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17">
-        <v>22.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="P12" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q12" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="R12" s="13"/>
-    </row>
-    <row r="13">
-      <c r="P13" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="R13" s="13"/>
-      <c r="T13" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="P14" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q14" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="R14" s="13"/>
-      <c r="T14" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="T15" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="27"/>
-    </row>
-    <row r="18">
-      <c r="T18" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="U18" s="32"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="13"/>
-    </row>
-    <row r="19">
-      <c r="P19" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q19" s="35"/>
-      <c r="T19" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="V19" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="W19" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="P20" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q20" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="R20" s="37"/>
-      <c r="T20" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="U20" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="V20" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="W20" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="P21" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="Q21" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="R21" s="37"/>
-      <c r="T21" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="U21" s="17">
-        <v>2.0</v>
-      </c>
-      <c r="V21" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="W21" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="P22" s="17">
-        <v>2.0</v>
-      </c>
-      <c r="Q22" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="R22" s="37"/>
-      <c r="T22" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="U22" s="17">
-        <v>3.0</v>
-      </c>
-      <c r="V22" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="W22" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="P23" s="17">
-        <v>3.0</v>
-      </c>
-      <c r="Q23" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="R23" s="37"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="AG23" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH23" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI23" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="P24" s="17">
-        <v>4.0</v>
-      </c>
-      <c r="Q24" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="R24" s="37"/>
-      <c r="T24" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="U24" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="V24" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="W24" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG24" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH24" s="8" t="s">
-        <v>142</v>
+      <c r="W24" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="T28" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="U28" s="33"/>
-      <c r="X28" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y28" s="33"/>
-      <c r="AA28" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD28" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF28" s="31" t="s">
-        <v>1</v>
+      <c r="T28" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="U28" s="42"/>
+      <c r="X28" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y28" s="42"/>
+      <c r="AA28" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD28" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="AF28" s="40" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="C29" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H29" s="32" t="s">
+      <c r="C29" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H29" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="J29" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="P29" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="T29" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="U29" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="X29" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y29" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA29" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="AB29" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC29" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD29" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF29" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG29" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="AH29" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI29" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="J29" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="P29" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="T29" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="U29" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="V29" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="X29" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y29" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA29" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB29" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="AC29" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD29" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF29" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG29" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH29" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="AI29" s="16" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D30" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="E30" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="J30" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="K30" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="P30" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q30" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>160</v>
+      <c r="C30" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="H30" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="J30" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="K30" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="P30" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q30" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="V30" s="4">
         <v>5.0</v>
       </c>
-      <c r="X30" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y30" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA30" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB30" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AC30" s="17">
+      <c r="X30" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y30" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA30" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB30" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC30" s="28">
         <v>225.0</v>
       </c>
-      <c r="AD30" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF30" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG30" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH30" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="AI30" s="17" t="s">
-        <v>169</v>
+      <c r="AD30" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF30" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG30" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="AH30" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="AI30" s="28" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="C31" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="D31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="41">
+      <c r="C31" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="50">
         <v>8.0</v>
       </c>
-      <c r="F31" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="H31" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="I31" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="J31" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="K31" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="43"/>
-      <c r="P31" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q31" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="R31" s="6">
+      <c r="F31" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="H31" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="I31" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="J31" s="54" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="L31" s="56"/>
+      <c r="M31" s="52"/>
+      <c r="P31" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q31" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="R31" s="9">
         <v>7.8</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="V31" s="4">
         <v>6.0</v>
       </c>
-      <c r="X31" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y31" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA31" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB31" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC31" s="17">
+      <c r="X31" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y31" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA31" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB31" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC31" s="28">
         <v>0.0</v>
       </c>
-      <c r="AD31" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF31" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG31" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="AH31" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="AI31" s="17" t="s">
-        <v>174</v>
+      <c r="AD31" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF31" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG31" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="AH31" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="AI31" s="28" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="C32" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="41">
+      <c r="C32" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="50">
         <v>6.0</v>
       </c>
-      <c r="F32" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="H32" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="I32" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="J32" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="P32" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q32" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="R32" s="6">
+      <c r="F32" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="J32" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="P32" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q32" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="R32" s="9">
         <v>8.0</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="V32" s="4">
         <v>7.0</v>
       </c>
-      <c r="X32" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="Y32" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA32" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB32" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="AC32" s="17">
+      <c r="X32" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y32" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA32" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB32" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC32" s="28">
         <v>125.0</v>
       </c>
-      <c r="AD32" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF32" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG32" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="AH32" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI32" s="17" t="s">
-        <v>169</v>
+      <c r="AD32" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF32" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG32" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="AH32" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI32" s="28" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="41">
+      <c r="C33" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="50">
         <v>9.0</v>
       </c>
-      <c r="F33" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="H33" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="I33" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="J33" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="P33" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q33" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="R33" s="6">
+      <c r="F33" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="I33" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="J33" s="54" t="s">
+        <v>210</v>
+      </c>
+      <c r="P33" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q33" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R33" s="9">
         <v>9.5</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="V33" s="4">
         <v>5.0</v>
       </c>
-      <c r="AA33" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB33" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC33" s="17">
+      <c r="AA33" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB33" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC33" s="28">
         <v>220.0</v>
       </c>
-      <c r="AD33" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="AF33" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="AG33" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="AH33" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="AI33" s="17" t="s">
-        <v>185</v>
+      <c r="AD33" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF33" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="AG33" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="AH33" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="AI33" s="28" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="C34" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="E34" s="41">
+      <c r="C34" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="50">
         <v>7.0</v>
       </c>
-      <c r="F34" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="P34" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q34" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="R34" s="6">
+      <c r="F34" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="P34" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q34" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="R34" s="9">
         <v>2.0</v>
       </c>
-      <c r="T34" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="U34" s="48" t="s">
-        <v>171</v>
+      <c r="T34" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="U34" s="57" t="s">
+        <v>218</v>
       </c>
       <c r="V34" s="4">
         <v>9.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="C35" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="D35" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="E35" s="41">
+      <c r="C35" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" s="50">
         <v>7.0</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="P35" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q35" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="R35" s="6">
+      <c r="F35" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="P35" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q35" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="R35" s="9">
         <v>4.6</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="C37" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="P37" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="AA37" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
-      <c r="AD37" s="27"/>
-      <c r="AE37" s="27"/>
-      <c r="AF37" s="27"/>
-      <c r="AG37" s="27"/>
-      <c r="AH37" s="27"/>
-      <c r="AI37" s="27"/>
-      <c r="AJ37" s="27"/>
+      <c r="C37" s="58" t="s">
+        <v>241</v>
+      </c>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="P37" s="58" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q37" s="38"/>
+      <c r="R37" s="38"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="38"/>
+      <c r="AA37" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="AB37" s="38"/>
+      <c r="AC37" s="38"/>
+      <c r="AD37" s="38"/>
+      <c r="AE37" s="38"/>
+      <c r="AF37" s="38"/>
+      <c r="AG37" s="38"/>
+      <c r="AH37" s="38"/>
+      <c r="AI37" s="38"/>
+      <c r="AJ37" s="38"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="C38" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA38" s="8" t="s">
-        <v>199</v>
+      <c r="C38" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA38" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="C39" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="P39" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA39" s="8" t="s">
-        <v>202</v>
+      <c r="C39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA39" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="C40" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="P40" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA40" s="8" t="s">
+      <c r="C40" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA40" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="C41" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA41" s="59" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="C42" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA42" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB42" s="60"/>
+      <c r="AC42" s="60"/>
+      <c r="AD42" s="60"/>
+      <c r="AE42" s="60"/>
+      <c r="AF42" s="60"/>
+      <c r="AG42" s="60"/>
+      <c r="AH42" s="60"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="C43" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="C44" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="O44" s="61" t="s">
+        <v>255</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="C45" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="O45" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q45" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="T45" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="C41" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA41" s="50" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="C42" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA42" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB42" s="51"/>
-      <c r="AC42" s="51"/>
-      <c r="AD42" s="51"/>
-      <c r="AE42" s="51"/>
-      <c r="AF42" s="51"/>
-      <c r="AG42" s="51"/>
-      <c r="AH42" s="51"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="C43" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="C44" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="O44" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="T44" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y44" s="8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="C45" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="O45" s="53" t="s">
-        <v>212</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q45" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="R45" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="T45" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="U45" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="V45" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y45" s="8" t="s">
-        <v>216</v>
+      <c r="U45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="C46" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="N46" s="8" t="s">
-        <v>218</v>
+      <c r="C46" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="O46" s="4">
         <v>1.0</v>
@@ -5350,14 +7335,14 @@
       <c r="P46" s="4">
         <v>1.0</v>
       </c>
-      <c r="Q46" s="54" t="s">
-        <v>219</v>
-      </c>
-      <c r="R46" s="54" t="s">
-        <v>220</v>
+      <c r="Q46" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="R46" s="63" t="s">
+        <v>266</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="U46" s="4">
         <v>1.0</v>
@@ -5365,16 +7350,16 @@
       <c r="V46" s="4">
         <v>8.0</v>
       </c>
-      <c r="Y46" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="AE46" s="8" t="s">
-        <v>222</v>
+      <c r="Y46" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="AE46" s="1" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="C47" s="8" t="s">
-        <v>223</v>
+      <c r="C47" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="O47" s="4">
         <v>2.0</v>
@@ -5382,14 +7367,14 @@
       <c r="P47" s="4">
         <v>2.0</v>
       </c>
-      <c r="Q47" s="54" t="s">
-        <v>224</v>
-      </c>
-      <c r="R47" s="54" t="s">
-        <v>225</v>
+      <c r="Q47" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="R47" s="63" t="s">
+        <v>271</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="U47" s="4">
         <v>2.0</v>
@@ -5397,16 +7382,16 @@
       <c r="V47" s="4">
         <v>8.0</v>
       </c>
-      <c r="Y47" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF47" s="8" t="s">
-        <v>226</v>
+      <c r="Y47" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF47" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="C48" s="55" t="s">
-        <v>227</v>
+      <c r="C48" s="64" t="s">
+        <v>273</v>
       </c>
       <c r="O48" s="4">
         <v>3.0</v>
@@ -5414,14 +7399,14 @@
       <c r="P48" s="4">
         <v>3.0</v>
       </c>
-      <c r="Q48" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="R48" s="54" t="s">
-        <v>229</v>
+      <c r="Q48" s="63" t="s">
+        <v>274</v>
+      </c>
+      <c r="R48" s="63" t="s">
+        <v>275</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="U48" s="4">
         <v>1.0</v>
@@ -5429,16 +7414,16 @@
       <c r="V48" s="4">
         <v>9.0</v>
       </c>
-      <c r="AE48" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF48" s="17" t="s">
-        <v>45</v>
+      <c r="AE48" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="AF48" s="28" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="49" ht="32.25" customHeight="1">
-      <c r="C49" s="56" t="s">
-        <v>230</v>
+      <c r="C49" s="65" t="s">
+        <v>276</v>
       </c>
       <c r="O49" s="4">
         <v>4.0</v>
@@ -5446,14 +7431,14 @@
       <c r="P49" s="4">
         <v>4.0</v>
       </c>
-      <c r="Q49" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="R49" s="54" t="s">
-        <v>232</v>
+      <c r="Q49" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="R49" s="63" t="s">
+        <v>278</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="U49" s="4">
         <v>1.0</v>
@@ -5461,11 +7446,11 @@
       <c r="V49" s="4">
         <v>9.0</v>
       </c>
-      <c r="AE49" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="AF49" s="17" t="s">
-        <v>52</v>
+      <c r="AE49" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF49" s="28" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -5475,17 +7460,17 @@
       <c r="P50" s="4">
         <v>5.0</v>
       </c>
-      <c r="Q50" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="R50" s="54" t="s">
-        <v>234</v>
-      </c>
-      <c r="AE50" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="AF50" s="17" t="s">
-        <v>60</v>
+      <c r="Q50" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="R50" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="AE50" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF50" s="28" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -5495,25 +7480,25 @@
       <c r="P51" s="4">
         <v>6.0</v>
       </c>
-      <c r="Q51" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="R51" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="AE51" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF51" s="17" t="s">
-        <v>66</v>
+      <c r="Q51" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="R51" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="AE51" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="AF51" s="28" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="C52" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="H52" s="32" t="s">
-        <v>150</v>
+      <c r="C52" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="H52" s="41" t="s">
+        <v>197</v>
       </c>
       <c r="O52" s="4">
         <v>7.0</v>
@@ -5521,40 +7506,40 @@
       <c r="P52" s="4">
         <v>7.0</v>
       </c>
-      <c r="Q52" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="R52" s="54" t="s">
-        <v>238</v>
-      </c>
-      <c r="AE52" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="AF52" s="17" t="s">
-        <v>187</v>
+      <c r="Q52" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="R52" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="AE52" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="AF52" s="28" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="C53" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="E53" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H53" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="I53" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>149</v>
+      <c r="C53" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D53" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="E53" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H53" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="O53" s="4">
         <v>8.0</v>
@@ -5562,65 +7547,65 @@
       <c r="P53" s="4">
         <v>8.0</v>
       </c>
-      <c r="Q53" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="R53" s="54" t="s">
-        <v>240</v>
+      <c r="Q53" s="63" t="s">
+        <v>285</v>
+      </c>
+      <c r="R53" s="63" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="C54" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E54" s="41">
+      <c r="C54" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="D54" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" s="50">
         <v>8.0</v>
       </c>
-      <c r="F54" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
+      <c r="F54" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H54" s="50"/>
+      <c r="I54" s="50"/>
       <c r="O54" s="4">
         <v>9.0</v>
       </c>
       <c r="P54" s="4">
         <v>1.0</v>
       </c>
-      <c r="Q54" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="R54" s="54" t="s">
-        <v>234</v>
+      <c r="Q54" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="R54" s="63" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="C55" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="E55" s="41">
+      <c r="C55" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="D55" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="50">
         <v>6.0</v>
       </c>
-      <c r="F55" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H55" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="I55" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>241</v>
+      <c r="F55" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H55" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="I55" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="O55" s="4">
         <v>10.0</v>
@@ -5628,34 +7613,34 @@
       <c r="P55" s="4">
         <v>2.0</v>
       </c>
-      <c r="Q55" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="R55" s="54" t="s">
-        <v>236</v>
+      <c r="Q55" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="R55" s="63" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="C56" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="D56" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="41">
+      <c r="C56" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="D56" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="E56" s="50">
         <v>9.0</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H56" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="I56" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>163</v>
+      <c r="F56" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H56" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="I56" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="O56" s="4">
         <v>11.0</v>
@@ -5663,25 +7648,25 @@
       <c r="P56" s="4">
         <v>3.0</v>
       </c>
-      <c r="Q56" s="54" t="s">
+      <c r="Q56" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="R56" s="63" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="C57" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" s="50" t="s">
         <v>237</v>
       </c>
-      <c r="R56" s="54" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="C57" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="E57" s="41">
+      <c r="E57" s="50">
         <v>7.0</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>178</v>
+      <c r="F57" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="O57" s="4">
         <v>12.0</v>
@@ -5689,25 +7674,25 @@
       <c r="P57" s="4">
         <v>4.0</v>
       </c>
-      <c r="Q57" s="54" t="s">
+      <c r="Q57" s="63" t="s">
+        <v>285</v>
+      </c>
+      <c r="R57" s="63" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="C58" s="50" t="s">
         <v>239</v>
       </c>
-      <c r="R57" s="54" t="s">
+      <c r="D58" s="50" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="C58" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="D58" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="E58" s="41">
+      <c r="E58" s="50">
         <v>7.0</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>172</v>
+      <c r="F58" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="O58" s="4">
         <v>13.0</v>
@@ -5715,11 +7700,11 @@
       <c r="P58" s="4">
         <v>5.0</v>
       </c>
-      <c r="Q58" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="R58" s="54" t="s">
-        <v>243</v>
+      <c r="Q58" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="R58" s="63" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
@@ -5729,11 +7714,11 @@
       <c r="P59" s="4">
         <v>6.0</v>
       </c>
-      <c r="Q59" s="54" t="s">
-        <v>244</v>
-      </c>
-      <c r="R59" s="54" t="s">
-        <v>245</v>
+      <c r="Q59" s="63" t="s">
+        <v>290</v>
+      </c>
+      <c r="R59" s="63" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -5743,11 +7728,11 @@
       <c r="P60" s="4">
         <v>7.0</v>
       </c>
-      <c r="Q60" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="R60" s="54" t="s">
-        <v>247</v>
+      <c r="Q60" s="63" t="s">
+        <v>292</v>
+      </c>
+      <c r="R60" s="63" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -5757,11 +7742,11 @@
       <c r="P61" s="4">
         <v>8.0</v>
       </c>
-      <c r="Q61" s="54" t="s">
-        <v>248</v>
-      </c>
-      <c r="R61" s="54" t="s">
-        <v>249</v>
+      <c r="Q61" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="R61" s="63" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1"/>
@@ -5774,116 +7759,116 @@
     <row r="69" ht="15.75" customHeight="1"/>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="Q71" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="W71" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="X71" s="33"/>
+      <c r="Q71" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="W71" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="X71" s="42"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="Q72" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="R72" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="S72" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="T72" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="W72" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="X72" s="17" t="s">
-        <v>82</v>
+      <c r="Q72" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="R72" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="S72" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="W72" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="X72" s="28" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="Q73" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="R73" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="S73" s="6">
+      <c r="Q73" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="R73" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="S73" s="9">
         <v>7.8</v>
       </c>
-      <c r="T73" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="W73" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="X73" s="17" t="s">
-        <v>164</v>
+      <c r="T73" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="W73" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="X73" s="28" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="Q74" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="R74" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="S74" s="6">
+      <c r="Q74" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="R74" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="S74" s="9">
         <v>8.0</v>
       </c>
-      <c r="T74" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="W74" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="X74" s="17" t="s">
-        <v>173</v>
+      <c r="T74" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="W74" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="X74" s="28" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="Q75" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="R75" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="S75" s="6">
+      <c r="Q75" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="R75" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S75" s="9">
         <v>9.5</v>
       </c>
-      <c r="T75" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="W75" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="X75" s="17" t="s">
-        <v>179</v>
+      <c r="T75" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="W75" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="X75" s="28" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="Q76" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="R76" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="S76" s="6">
+      <c r="Q76" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="R76" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="S76" s="9">
         <v>2.0</v>
       </c>
-      <c r="T76" s="8" t="s">
-        <v>172</v>
+      <c r="T76" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="Q77" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="R77" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="S77" s="6">
+      <c r="Q77" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="R77" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="S77" s="9">
         <v>4.6</v>
       </c>
     </row>
@@ -6828,7 +8813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
@@ -6847,14 +8832,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="4" ht="18.0" customHeight="1">
-      <c r="B4" s="57"/>
+      <c r="B4" s="66"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6869,28 +8854,28 @@
       <c r="N4" s="2"/>
     </row>
     <row r="5" ht="18.0" customHeight="1">
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="B6" s="58"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="58"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="67"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -6900,24 +8885,24 @@
     </row>
     <row r="7" ht="18.0" customHeight="1">
       <c r="B7" s="4"/>
-      <c r="C7" s="6"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="60"/>
+      <c r="H7" s="69"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="60"/>
+      <c r="K7" s="69"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="6"/>
+      <c r="N7" s="9"/>
     </row>
     <row r="8" ht="18.0" customHeight="1">
       <c r="B8" s="4"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -6926,14 +8911,14 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="6"/>
+      <c r="N8" s="9"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
       <c r="B9" s="4"/>
-      <c r="C9" s="6"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="60"/>
+      <c r="F9" s="69"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -6941,11 +8926,11 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="6"/>
+      <c r="N9" s="9"/>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="B10" s="17"/>
-      <c r="C10" s="6"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -6956,11 +8941,11 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="6"/>
+      <c r="N10" s="9"/>
     </row>
     <row r="11" ht="18.0" customHeight="1">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -6971,11 +8956,11 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="6"/>
+      <c r="N11" s="9"/>
     </row>
     <row r="12" ht="18.0" customHeight="1">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -6986,14 +8971,14 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="6"/>
+      <c r="N12" s="9"/>
     </row>
     <row r="13" ht="18.0" customHeight="1">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="60"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -7001,11 +8986,11 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="6"/>
+      <c r="N13" s="9"/>
     </row>
     <row r="14" ht="18.0" customHeight="1">
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -7016,11 +9001,11 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="6"/>
+      <c r="N14" s="9"/>
     </row>
     <row r="15" ht="18.0" customHeight="1">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -7031,11 +9016,11 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="6"/>
+      <c r="N15" s="9"/>
     </row>
     <row r="16" ht="18.0" customHeight="1">
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -7046,11 +9031,11 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="9"/>
     </row>
     <row r="17" ht="18.0" customHeight="1">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -7061,11 +9046,11 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="6"/>
+      <c r="N17" s="9"/>
     </row>
     <row r="18" ht="18.0" customHeight="1">
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -7076,11 +9061,11 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="6"/>
+      <c r="N18" s="9"/>
     </row>
     <row r="19" ht="18.0" customHeight="1">
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -7091,11 +9076,11 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="6"/>
+      <c r="N19" s="9"/>
     </row>
     <row r="20" ht="18.0" customHeight="1">
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -7106,28 +9091,28 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="6"/>
+      <c r="N20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="B22" s="8" t="s">
-        <v>250</v>
+      <c r="B22" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="B23" s="8" t="s">
-        <v>251</v>
+      <c r="B23" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="B24" s="8" t="s">
-        <v>252</v>
+      <c r="B24" s="1" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="B26" s="8" t="s">
-        <v>253</v>
+      <c r="B26" s="1" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
